--- a/AAII_Financials/Yearly/XP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XP_YR_FIN.xlsx
@@ -1038,13 +1038,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>33000</v>
+        <v>23700</v>
       </c>
       <c r="E15" s="3">
-        <v>21500</v>
+        <v>19500</v>
       </c>
       <c r="F15" s="3">
-        <v>21600</v>
+        <v>18400</v>
       </c>
       <c r="G15" s="3">
         <v>9500</v>
@@ -1267,13 +1267,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1039000</v>
+        <v>1029600</v>
       </c>
       <c r="E21" s="3">
-        <v>835500</v>
+        <v>833400</v>
       </c>
       <c r="F21" s="3">
-        <v>849000</v>
+        <v>845800</v>
       </c>
       <c r="G21" s="3">
         <v>666600</v>
